--- a/Project_ETF/ETF_Investment_Portfolio/0050/ETF_Investment_Portfolio_20260708.xlsx
+++ b/Project_ETF/ETF_Investment_Portfolio/0050/ETF_Investment_Portfolio_20260708.xlsx
@@ -1019,17 +1019,17 @@
     <row r="40">
       <c r="A40" s="3" t="inlineStr">
         <is>
-          <t>202607TX</t>
+          <t>2886</t>
         </is>
       </c>
       <c r="B40" s="3" t="inlineStr">
         <is>
-          <t>臺股期貨</t>
+          <t>兆豐金</t>
         </is>
       </c>
       <c r="C40" s="4" t="inlineStr">
         <is>
-          <t>1,318</t>
+          <t>256,155,162</t>
         </is>
       </c>
       <c r="D40" s="4" t="inlineStr">
@@ -1041,17 +1041,17 @@
     <row r="41">
       <c r="A41" s="3" t="inlineStr">
         <is>
-          <t>2886</t>
+          <t>202607TX</t>
         </is>
       </c>
       <c r="B41" s="3" t="inlineStr">
         <is>
-          <t>兆豐金</t>
+          <t>臺股期貨</t>
         </is>
       </c>
       <c r="C41" s="4" t="inlineStr">
         <is>
-          <t>256,155,162</t>
+          <t>1,318</t>
         </is>
       </c>
       <c r="D41" s="4" t="inlineStr">
@@ -1217,17 +1217,17 @@
     <row r="49">
       <c r="A49" s="3" t="inlineStr">
         <is>
-          <t>2059</t>
+          <t>2408</t>
         </is>
       </c>
       <c r="B49" s="3" t="inlineStr">
         <is>
-          <t>川湖</t>
+          <t>南亞科</t>
         </is>
       </c>
       <c r="C49" s="4" t="inlineStr">
         <is>
-          <t>1,194,852</t>
+          <t>24,724,158</t>
         </is>
       </c>
       <c r="D49" s="4" t="inlineStr">
@@ -1239,17 +1239,17 @@
     <row r="50">
       <c r="A50" s="3" t="inlineStr">
         <is>
-          <t>2408</t>
+          <t>2059</t>
         </is>
       </c>
       <c r="B50" s="3" t="inlineStr">
         <is>
-          <t>南亞科</t>
+          <t>川湖</t>
         </is>
       </c>
       <c r="C50" s="4" t="inlineStr">
         <is>
-          <t>24,724,158</t>
+          <t>1,194,852</t>
         </is>
       </c>
       <c r="D50" s="4" t="inlineStr">
